--- a/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_main.xlsx
+++ b/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_main.xlsx
@@ -40,88 +40,88 @@
     <t>Variance</t>
   </si>
   <si>
+    <t>ErCo2.68In0.32</t>
+  </si>
+  <si>
+    <t>CoIn3</t>
+  </si>
+  <si>
     <t>Er2CoIn8</t>
   </si>
   <si>
+    <t>ErCoIn5</t>
+  </si>
+  <si>
+    <t>Er11Co4In9</t>
+  </si>
+  <si>
+    <t>ErCo4In</t>
+  </si>
+  <si>
+    <t>Er6Co2.19In0.81</t>
+  </si>
+  <si>
+    <t>Er14Co3In3</t>
+  </si>
+  <si>
+    <t>Er8CoIn3</t>
+  </si>
+  <si>
+    <t>Er3Co1.87In4</t>
+  </si>
+  <si>
+    <t>CoIn2</t>
+  </si>
+  <si>
+    <t>Er14Co2In3</t>
+  </si>
+  <si>
     <t>Er10Co9In20</t>
   </si>
   <si>
-    <t>Er11Co4In9</t>
-  </si>
-  <si>
-    <t>CoIn3</t>
-  </si>
-  <si>
-    <t>ErCo4In</t>
-  </si>
-  <si>
-    <t>CoIn2</t>
-  </si>
-  <si>
-    <t>Er6Co2.19In0.81</t>
-  </si>
-  <si>
-    <t>Er8CoIn3</t>
-  </si>
-  <si>
-    <t>ErCoIn5</t>
-  </si>
-  <si>
-    <t>Er3Co1.87In4</t>
-  </si>
-  <si>
-    <t>ErCo2.68In0.32</t>
-  </si>
-  <si>
-    <t>Er14Co3In3</t>
-  </si>
-  <si>
-    <t>Er14Co2In3</t>
+    <t>PuNi3</t>
+  </si>
+  <si>
+    <t>IrIn3</t>
   </si>
   <si>
     <t>Ho2CoGa8</t>
   </si>
   <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>Nd11Pd4In9</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
+    <t>Ho6Co2Ga</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
+  </si>
+  <si>
+    <t>Pr8CoGa3</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
+  </si>
+  <si>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>Mg2Cu</t>
+  </si>
+  <si>
+    <t>Lu14Co2In3</t>
+  </si>
+  <si>
     <t>Ho10Ni9In20</t>
-  </si>
-  <si>
-    <t>Nd11Pd4In9</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>MgCu4Sn</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
-  </si>
-  <si>
-    <t>Ho6Co2Ga</t>
-  </si>
-  <si>
-    <t>Pr8CoGa3</t>
-  </si>
-  <si>
-    <t>IrIn3</t>
-  </si>
-  <si>
-    <t>HoCoGa5</t>
-  </si>
-  <si>
-    <t>Lu3Co2In4</t>
-  </si>
-  <si>
-    <t>PuNi3</t>
-  </si>
-  <si>
-    <t>Gd14Co3In2.7</t>
-  </si>
-  <si>
-    <t>Lu14Co2In3</t>
   </si>
   <si>
     <t>Er-Er</t>
@@ -557,16 +557,16 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>2.864</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -577,16 +577,16 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -597,16 +597,16 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>2.687</v>
+        <v>2.471</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>3.157</v>
+        <v>2.471</v>
       </c>
       <c r="G6">
-        <v>0.095</v>
+        <v>0.016</v>
       </c>
       <c r="H6">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -637,16 +637,16 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>3.222</v>
+        <v>2.864</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -683,19 +683,19 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>2.962</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -723,19 +723,19 @@
         <v>39</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>2.685</v>
+        <v>2.608</v>
       </c>
       <c r="G12">
-        <v>0.035</v>
+        <v>0.011</v>
       </c>
       <c r="H12">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -809,19 +809,19 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>2.831</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -849,19 +849,19 @@
         <v>39</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>2.984</v>
+        <v>2.687</v>
       </c>
       <c r="G19">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -869,19 +869,19 @@
         <v>40</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2.947</v>
+        <v>3.157</v>
       </c>
       <c r="G20">
-        <v>0.029</v>
+        <v>0.095</v>
       </c>
       <c r="H20">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -889,19 +889,19 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>3.179</v>
+        <v>3.222</v>
       </c>
       <c r="G21">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -975,19 +975,19 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26">
-        <v>2.62</v>
+        <v>2.569</v>
       </c>
       <c r="G26">
-        <v>0.032</v>
+        <v>0.173</v>
       </c>
       <c r="H26">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3.199</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>3.079</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1061,19 +1061,19 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>2.922</v>
+        <v>2.831</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1081,13 +1081,13 @@
         <v>38</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>2.492</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1101,19 +1101,19 @@
         <v>39</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>2.922</v>
+        <v>2.984</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1121,19 +1121,19 @@
         <v>40</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>2.947</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1141,24 +1141,24 @@
         <v>41</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>3.179</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
@@ -1187,13 +1187,13 @@
         <v>37</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>2.922</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1207,13 +1207,13 @@
         <v>38</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>2.492</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1227,16 +1227,16 @@
         <v>39</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>2.597</v>
+        <v>2.922</v>
       </c>
       <c r="G40">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
         <v>27</v>
@@ -1359,13 +1359,13 @@
         <v>2</v>
       </c>
       <c r="F47">
-        <v>2.708</v>
+        <v>2.597</v>
       </c>
       <c r="G47">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
       <c r="H47">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1565,19 +1565,19 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F59">
-        <v>2.807</v>
+        <v>2.762</v>
       </c>
       <c r="G59">
-        <v>0.066</v>
+        <v>0.171</v>
       </c>
       <c r="H59">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -1585,13 +1585,13 @@
         <v>38</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>2.964</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -1605,13 +1605,13 @@
         <v>39</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>2.964</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -1625,19 +1625,19 @@
         <v>40</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>3.104</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -1645,24 +1645,24 @@
         <v>41</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63">
-        <v>3.179</v>
+        <v>3.183</v>
       </c>
       <c r="G63">
-        <v>0.202</v>
+        <v>0.12</v>
       </c>
       <c r="H63">
-        <v>0.041</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
         <v>30</v>
@@ -1691,19 +1691,19 @@
         <v>37</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>2.807</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -1731,16 +1731,16 @@
         <v>39</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>2.608</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -1771,24 +1771,24 @@
         <v>41</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>3.179</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B72" t="s">
         <v>31</v>
@@ -1857,19 +1857,19 @@
         <v>39</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>2</v>
       </c>
       <c r="F75">
-        <v>2.569</v>
+        <v>2.62</v>
       </c>
       <c r="G75">
-        <v>0.173</v>
+        <v>0.032</v>
       </c>
       <c r="H75">
-        <v>0.03</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -1880,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>3.199</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -1897,19 +1897,19 @@
         <v>41</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>3.079</v>
+        <v>0</v>
       </c>
       <c r="G77">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>0.029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2069,16 +2069,16 @@
         <v>37</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>2.864</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -2089,16 +2089,16 @@
         <v>38</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>2.471</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -2115,13 +2115,13 @@
         <v>2</v>
       </c>
       <c r="F89">
-        <v>2.471</v>
+        <v>2.708</v>
       </c>
       <c r="G89">
-        <v>0.016</v>
+        <v>0.037</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2129,16 +2129,16 @@
         <v>40</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>2.471</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -2149,16 +2149,16 @@
         <v>41</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>2.864</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -2195,19 +2195,19 @@
         <v>37</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F94">
-        <v>2.762</v>
+        <v>2.72</v>
       </c>
       <c r="G94">
-        <v>0.171</v>
+        <v>0.068</v>
       </c>
       <c r="H94">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -2215,13 +2215,13 @@
         <v>38</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>2.964</v>
+        <v>0</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="F96">
-        <v>2.964</v>
+        <v>2.975</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -2255,19 +2255,19 @@
         <v>40</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97">
-        <v>3.104</v>
+        <v>2.999</v>
       </c>
       <c r="G97">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>0.018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2275,19 +2275,19 @@
         <v>41</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98">
-        <v>3.183</v>
+        <v>3.203</v>
       </c>
       <c r="G98">
-        <v>0.12</v>
+        <v>0.111</v>
       </c>
       <c r="H98">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -2321,19 +2321,19 @@
         <v>37</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F101">
-        <v>2.72</v>
+        <v>2.962</v>
       </c>
       <c r="G101">
-        <v>0.068</v>
+        <v>0.052</v>
       </c>
       <c r="H101">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -2361,19 +2361,19 @@
         <v>39</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F103">
-        <v>2.975</v>
+        <v>2.685</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -2381,13 +2381,13 @@
         <v>40</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>2.999</v>
+        <v>0</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -2401,19 +2401,19 @@
         <v>41</v>
       </c>
       <c r="D105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>3.203</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_main.xlsx
+++ b/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_main.xlsx
@@ -40,88 +40,88 @@
     <t>Variance</t>
   </si>
   <si>
+    <t>Er14Co2In3</t>
+  </si>
+  <si>
     <t>ErCo2.68In0.32</t>
   </si>
   <si>
+    <t>Er2CoIn8</t>
+  </si>
+  <si>
+    <t>Er10Co9In20</t>
+  </si>
+  <si>
+    <t>CoIn2</t>
+  </si>
+  <si>
+    <t>Er14Co3In3</t>
+  </si>
+  <si>
     <t>CoIn3</t>
   </si>
   <si>
-    <t>Er2CoIn8</t>
-  </si>
-  <si>
     <t>ErCoIn5</t>
   </si>
   <si>
+    <t>ErCo4In</t>
+  </si>
+  <si>
+    <t>Er6Co2.19In0.81</t>
+  </si>
+  <si>
+    <t>Er3Co1.87In4</t>
+  </si>
+  <si>
     <t>Er11Co4In9</t>
   </si>
   <si>
-    <t>ErCo4In</t>
-  </si>
-  <si>
-    <t>Er6Co2.19In0.81</t>
-  </si>
-  <si>
-    <t>Er14Co3In3</t>
-  </si>
-  <si>
     <t>Er8CoIn3</t>
   </si>
   <si>
-    <t>Er3Co1.87In4</t>
-  </si>
-  <si>
-    <t>CoIn2</t>
-  </si>
-  <si>
-    <t>Er14Co2In3</t>
-  </si>
-  <si>
-    <t>Er10Co9In20</t>
+    <t>Lu14Co2In3</t>
   </si>
   <si>
     <t>PuNi3</t>
   </si>
   <si>
+    <t>Ho2CoGa8</t>
+  </si>
+  <si>
+    <t>Ho10Ni9In20</t>
+  </si>
+  <si>
+    <t>Mg2Cu</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
+  </si>
+  <si>
+    <t>Ho6Co2Ga</t>
+  </si>
+  <si>
     <t>IrIn3</t>
   </si>
   <si>
-    <t>Ho2CoGa8</t>
-  </si>
-  <si>
-    <t>HoCoGa5</t>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
   </si>
   <si>
     <t>Nd11Pd4In9</t>
   </si>
   <si>
-    <t>MgCu4Sn</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>Ho6Co2Ga</t>
-  </si>
-  <si>
-    <t>Gd14Co3In2.7</t>
-  </si>
-  <si>
     <t>Pr8CoGa3</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>Lu3Co2In4</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
-  </si>
-  <si>
-    <t>Lu14Co2In3</t>
-  </si>
-  <si>
-    <t>Ho10Ni9In20</t>
   </si>
   <si>
     <t>Er-Er</t>
@@ -557,19 +557,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2.864</v>
+        <v>2.72</v>
       </c>
       <c r="G3">
-        <v>0.007</v>
+        <v>0.068</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -577,16 +577,16 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2.471</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -597,16 +597,16 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2.471</v>
+        <v>2.975</v>
       </c>
       <c r="G5">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -617,16 +617,16 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>2.471</v>
+        <v>2.999</v>
       </c>
       <c r="G6">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -637,19 +637,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>2.864</v>
+        <v>3.203</v>
       </c>
       <c r="G7">
-        <v>0.007</v>
+        <v>0.111</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -683,16 +683,16 @@
         <v>37</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2.864</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -703,16 +703,16 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -726,13 +726,13 @@
         <v>2</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>2.608</v>
+        <v>2.471</v>
       </c>
       <c r="G12">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -743,16 +743,16 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -763,16 +763,16 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2.864</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -935,19 +935,19 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2.962</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -975,19 +975,19 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>2.569</v>
+        <v>2.685</v>
       </c>
       <c r="G26">
-        <v>0.173</v>
+        <v>0.035</v>
       </c>
       <c r="H26">
-        <v>0.03</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>3.199</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>3.079</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0.029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1061,19 +1061,19 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>2.831</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>0.007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1104,16 +1104,16 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>2.984</v>
+        <v>2.708</v>
       </c>
       <c r="G33">
-        <v>0.14</v>
+        <v>0.037</v>
       </c>
       <c r="H33">
-        <v>0.02</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1121,19 +1121,19 @@
         <v>40</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2.947</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1141,19 +1141,19 @@
         <v>41</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>3.179</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1187,19 +1187,19 @@
         <v>37</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>2.922</v>
+        <v>2.762</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1213,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>2.492</v>
+        <v>2.964</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>2.922</v>
+        <v>2.964</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1247,19 +1247,19 @@
         <v>40</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>3.104</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1267,24 +1267,24 @@
         <v>41</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>3.183</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
         <v>27</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
         <v>28</v>
@@ -1439,19 +1439,19 @@
         <v>37</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>2.834</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1459,19 +1459,19 @@
         <v>38</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>2.297</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1479,19 +1479,19 @@
         <v>39</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>2.569</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1502,10 +1502,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>3.199</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -1519,24 +1519,24 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>3.124</v>
+        <v>3.079</v>
       </c>
       <c r="G56">
-        <v>0.228</v>
+        <v>0.17</v>
       </c>
       <c r="H56">
-        <v>0.052</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
         <v>29</v>
@@ -1565,19 +1565,19 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2.762</v>
+        <v>2.922</v>
       </c>
       <c r="G59">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>0.029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -1591,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="F60">
-        <v>2.964</v>
+        <v>2.492</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>2.964</v>
+        <v>2.922</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -1625,19 +1625,19 @@
         <v>40</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>3.104</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>0.018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -1645,24 +1645,24 @@
         <v>41</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>3.183</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
         <v>30</v>
@@ -1691,19 +1691,19 @@
         <v>37</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>2.807</v>
+        <v>2.834</v>
       </c>
       <c r="G66">
-        <v>0.066</v>
+        <v>0.11</v>
       </c>
       <c r="H66">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -1711,19 +1711,19 @@
         <v>38</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>2.297</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -1774,21 +1774,21 @@
         <v>2</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>3.179</v>
+        <v>3.124</v>
       </c>
       <c r="G70">
-        <v>0.202</v>
+        <v>0.228</v>
       </c>
       <c r="H70">
-        <v>0.041</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s">
         <v>31</v>
@@ -1860,16 +1860,16 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F75">
-        <v>2.62</v>
+        <v>2.608</v>
       </c>
       <c r="G75">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="H75">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B79" t="s">
         <v>32</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B86" t="s">
         <v>33</v>
@@ -2115,10 +2115,10 @@
         <v>2</v>
       </c>
       <c r="F89">
-        <v>2.708</v>
+        <v>2.62</v>
       </c>
       <c r="G89">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="H89">
         <v>0.001</v>
@@ -2198,16 +2198,16 @@
         <v>3</v>
       </c>
       <c r="E94">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F94">
-        <v>2.72</v>
+        <v>2.831</v>
       </c>
       <c r="G94">
-        <v>0.068</v>
+        <v>0.081</v>
       </c>
       <c r="H94">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -2235,19 +2235,19 @@
         <v>39</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F96">
-        <v>2.975</v>
+        <v>2.984</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2258,16 +2258,16 @@
         <v>1</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97">
-        <v>2.999</v>
+        <v>2.947</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2275,19 +2275,19 @@
         <v>41</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98">
         <v>4</v>
       </c>
       <c r="F98">
-        <v>3.203</v>
+        <v>3.179</v>
       </c>
       <c r="G98">
-        <v>0.111</v>
+        <v>0.031</v>
       </c>
       <c r="H98">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -2321,19 +2321,19 @@
         <v>37</v>
       </c>
       <c r="D101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E101">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F101">
-        <v>2.962</v>
+        <v>2.807</v>
       </c>
       <c r="G101">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
       <c r="H101">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -2361,19 +2361,19 @@
         <v>39</v>
       </c>
       <c r="D103">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E103">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F103">
-        <v>2.685</v>
+        <v>0</v>
       </c>
       <c r="G103">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="H103">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -2401,19 +2401,19 @@
         <v>41</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>3.179</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>0.041</v>
       </c>
     </row>
   </sheetData>
